--- a/artfynd/A 35138-2023 artfynd.xlsx
+++ b/artfynd/A 35138-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35138-2023 artfynd.xlsx
+++ b/artfynd/A 35138-2023 artfynd.xlsx
@@ -1400,7 +1400,7 @@
         <v>112928476</v>
       </c>
       <c r="B8" t="n">
-        <v>96560</v>
+        <v>96562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
